--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39484,10 +39484,10 @@
         <v>46276.5625</v>
       </c>
       <c r="B1505" t="n">
-        <v>4475417</v>
+        <v>4487100</v>
       </c>
       <c r="C1505" t="n">
-        <v>333.429992675781</v>
+        <v>333.480010986328</v>
       </c>
       <c r="D1505" t="n">
         <v>323.420013427734</v>
@@ -39502,6 +39502,32 @@
         <v>328.989990234375</v>
       </c>
       <c r="H1505" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>4775160</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>336.484985351562</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>319</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>329</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>332.350006103516</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>332.350006103516</v>
+      </c>
+      <c r="H1506" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39510,7 +39510,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1506" t="n">
-        <v>4775160</v>
+        <v>4775900</v>
       </c>
       <c r="C1506" t="n">
         <v>336.484985351562</v>
@@ -39528,6 +39528,32 @@
         <v>332.350006103516</v>
       </c>
       <c r="H1506" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1507" t="n">
+        <v>3973273</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>328.660003662109</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>318.500091552734</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>324.890014648438</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>322.980010986328</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>322.980010986328</v>
+      </c>
+      <c r="H1507" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39536,13 +39536,13 @@
         <v>46280.5625</v>
       </c>
       <c r="B1507" t="n">
-        <v>3973273</v>
+        <v>3978200</v>
       </c>
       <c r="C1507" t="n">
         <v>328.660003662109</v>
       </c>
       <c r="D1507" t="n">
-        <v>318.500091552734</v>
+        <v>318.5</v>
       </c>
       <c r="E1507" t="n">
         <v>324.890014648438</v>
@@ -39554,6 +39554,32 @@
         <v>322.980010986328</v>
       </c>
       <c r="H1507" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1508" t="n">
+        <v>3755657</v>
+      </c>
+      <c r="C1508" t="n">
+        <v>338</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>317.450012207031</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>318.140014648438</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>331.019989013672</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>331.019989013672</v>
+      </c>
+      <c r="H1508" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39562,7 +39562,7 @@
         <v>46281.5625</v>
       </c>
       <c r="B1508" t="n">
-        <v>3755657</v>
+        <v>3757600</v>
       </c>
       <c r="C1508" t="n">
         <v>338</v>
@@ -39580,6 +39580,32 @@
         <v>331.019989013672</v>
       </c>
       <c r="H1508" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1509" t="n">
+        <v>4286627</v>
+      </c>
+      <c r="C1509" t="n">
+        <v>344.660003662109</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>328.773986816406</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>334</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>338.390014648438</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>338.390014648438</v>
+      </c>
+      <c r="H1509" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39588,7 +39588,7 @@
         <v>46282.5625</v>
       </c>
       <c r="B1509" t="n">
-        <v>4286627</v>
+        <v>4288200</v>
       </c>
       <c r="C1509" t="n">
         <v>344.660003662109</v>
@@ -39606,6 +39606,32 @@
         <v>338.390014648438</v>
       </c>
       <c r="H1509" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1510" t="n">
+        <v>4245045</v>
+      </c>
+      <c r="C1510" t="n">
+        <v>339.269989013672</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>330.714996337891</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>338.609985351562</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>332.429992675781</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>332.429992675781</v>
+      </c>
+      <c r="H1510" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39614,13 +39614,13 @@
         <v>46283.5625</v>
       </c>
       <c r="B1510" t="n">
-        <v>4245045</v>
+        <v>4313300</v>
       </c>
       <c r="C1510" t="n">
-        <v>339.269989013672</v>
+        <v>340.309997558594</v>
       </c>
       <c r="D1510" t="n">
-        <v>330.714996337891</v>
+        <v>330.140014648438</v>
       </c>
       <c r="E1510" t="n">
         <v>338.609985351562</v>
@@ -39632,6 +39632,32 @@
         <v>332.429992675781</v>
       </c>
       <c r="H1510" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1511" t="n">
+        <v>3686505</v>
+      </c>
+      <c r="C1511" t="n">
+        <v>339.529998779297</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>329.130004882812</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>335.630004882812</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>339.390014648438</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>339.390014648438</v>
+      </c>
+      <c r="H1511" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39640,7 +39640,7 @@
         <v>46286.5625</v>
       </c>
       <c r="B1511" t="n">
-        <v>3686505</v>
+        <v>3690300</v>
       </c>
       <c r="C1511" t="n">
         <v>339.529998779297</v>
@@ -39658,6 +39658,32 @@
         <v>339.390014648438</v>
       </c>
       <c r="H1511" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1512" t="n">
+        <v>4957023</v>
+      </c>
+      <c r="C1512" t="n">
+        <v>346.791198730469</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>333.679992675781</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>345.700012207031</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>336.589996337891</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>336.589996337891</v>
+      </c>
+      <c r="H1512" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -35130,13 +35130,13 @@
         <v>46288.5625</v>
       </c>
       <c r="B1512" t="n">
-        <v>4033810</v>
+        <v>4037300</v>
       </c>
       <c r="C1512" t="n">
         <v>348.609985351562</v>
       </c>
       <c r="D1512" t="n">
-        <v>333.170013427734</v>
+        <v>333.160003662109</v>
       </c>
       <c r="E1512" t="n">
         <v>338.149993896484</v>
@@ -35145,6 +35145,29 @@
         <v>334.809997558594</v>
       </c>
       <c r="G1512" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1513" t="n">
+        <v>2792208</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>337.644989013672</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>328.209991455078</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>332.850006103516</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>334</v>
+      </c>
+      <c r="G1513" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39744,7 +39744,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1515" t="n">
-        <v>3019283</v>
+        <v>3025900</v>
       </c>
       <c r="C1515" t="n">
         <v>347.220001220703</v>
@@ -39762,6 +39762,32 @@
         <v>335.940002441406</v>
       </c>
       <c r="H1515" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1516" t="n">
+        <v>4522291</v>
+      </c>
+      <c r="C1516" t="n">
+        <v>333.720001220703</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>316.630004882812</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>320.010009765625</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>328.119995117188</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>328.119995117188</v>
+      </c>
+      <c r="H1516" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39770,7 +39770,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1516" t="n">
-        <v>4522291</v>
+        <v>4523500</v>
       </c>
       <c r="C1516" t="n">
         <v>333.720001220703</v>
@@ -39788,6 +39788,32 @@
         <v>328.119995117188</v>
       </c>
       <c r="H1516" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1517" t="n">
+        <v>5701377</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>333.410003662109</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>324.170013427734</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>331.179992675781</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>330.309997558594</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>330.309997558594</v>
+      </c>
+      <c r="H1517" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39796,7 +39796,7 @@
         <v>46294.5625</v>
       </c>
       <c r="B1517" t="n">
-        <v>5701377</v>
+        <v>5712000</v>
       </c>
       <c r="C1517" t="n">
         <v>333.410003662109</v>
@@ -39814,6 +39814,32 @@
         <v>330.309997558594</v>
       </c>
       <c r="H1517" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1518" t="n">
+        <v>5704820</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>348.244995117188</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>331</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>331</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>339.559997558594</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>339.559997558594</v>
+      </c>
+      <c r="H1518" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39822,13 +39822,13 @@
         <v>46295.5625</v>
       </c>
       <c r="B1518" t="n">
-        <v>5704820</v>
+        <v>5705400</v>
       </c>
       <c r="C1518" t="n">
-        <v>348.244995117188</v>
+        <v>348.279998779297</v>
       </c>
       <c r="D1518" t="n">
-        <v>331</v>
+        <v>330.549987792969</v>
       </c>
       <c r="E1518" t="n">
         <v>331</v>
@@ -39840,6 +39840,32 @@
         <v>339.559997558594</v>
       </c>
       <c r="H1518" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1519" t="n">
+        <v>3604951</v>
+      </c>
+      <c r="C1519" t="n">
+        <v>344.420013427734</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>336.314086914062</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>341.570007324219</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>341.989990234375</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>341.989990234375</v>
+      </c>
+      <c r="H1519" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39848,13 +39848,13 @@
         <v>46296.5625</v>
       </c>
       <c r="B1519" t="n">
-        <v>3604951</v>
+        <v>3605500</v>
       </c>
       <c r="C1519" t="n">
         <v>344.420013427734</v>
       </c>
       <c r="D1519" t="n">
-        <v>336.314086914062</v>
+        <v>336.313995361328</v>
       </c>
       <c r="E1519" t="n">
         <v>341.570007324219</v>
@@ -39866,6 +39866,32 @@
         <v>341.989990234375</v>
       </c>
       <c r="H1519" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1520" t="n">
+        <v>3301495</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>347.119995117188</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>333.200012207031</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>344</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>341.040008544922</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>341.040008544922</v>
+      </c>
+      <c r="H1520" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39874,10 +39874,10 @@
         <v>46297.5625</v>
       </c>
       <c r="B1520" t="n">
-        <v>3301495</v>
+        <v>3303300</v>
       </c>
       <c r="C1520" t="n">
-        <v>347.119995117188</v>
+        <v>347.200012207031</v>
       </c>
       <c r="D1520" t="n">
         <v>333.200012207031</v>
@@ -39892,6 +39892,32 @@
         <v>341.040008544922</v>
       </c>
       <c r="H1520" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1521" t="n">
+        <v>3265500</v>
+      </c>
+      <c r="C1521" t="n">
+        <v>343</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>337.869995117188</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>342</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>338.989990234375</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>338.989990234375</v>
+      </c>
+      <c r="H1521" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39900,7 +39900,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1521" t="n">
-        <v>3265500</v>
+        <v>3268100</v>
       </c>
       <c r="C1521" t="n">
         <v>343</v>
@@ -39918,6 +39918,32 @@
         <v>338.989990234375</v>
       </c>
       <c r="H1521" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1522" t="n">
+        <v>3549937</v>
+      </c>
+      <c r="C1522" t="n">
+        <v>349</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>335.109985351562</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>339.700012207031</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>335.950012207031</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>335.950012207031</v>
+      </c>
+      <c r="H1522" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39926,7 +39926,7 @@
         <v>46301.5625</v>
       </c>
       <c r="B1522" t="n">
-        <v>3549937</v>
+        <v>3551500</v>
       </c>
       <c r="C1522" t="n">
         <v>349</v>
@@ -39944,6 +39944,32 @@
         <v>335.950012207031</v>
       </c>
       <c r="H1522" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1523" t="n">
+        <v>2441528</v>
+      </c>
+      <c r="C1523" t="n">
+        <v>341.619995117188</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>332</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>333.420013427734</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>332.850006103516</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>332.850006103516</v>
+      </c>
+      <c r="H1523" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39952,7 +39952,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1523" t="n">
-        <v>2441528</v>
+        <v>2470700</v>
       </c>
       <c r="C1523" t="n">
         <v>341.619995117188</v>
@@ -39970,6 +39970,32 @@
         <v>332.850006103516</v>
       </c>
       <c r="H1523" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1524" t="n">
+        <v>3986549</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>344.659912109375</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>332.279998779297</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>332.109985351562</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>343.399993896484</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>343.399993896484</v>
+      </c>
+      <c r="H1524" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -39978,13 +39978,13 @@
         <v>46303.5625</v>
       </c>
       <c r="B1524" t="n">
-        <v>3986549</v>
+        <v>3989000</v>
       </c>
       <c r="C1524" t="n">
-        <v>344.659912109375</v>
+        <v>344.660003662109</v>
       </c>
       <c r="D1524" t="n">
-        <v>332.279998779297</v>
+        <v>332.109985351562</v>
       </c>
       <c r="E1524" t="n">
         <v>332.109985351562</v>
@@ -39996,6 +39996,32 @@
         <v>343.399993896484</v>
       </c>
       <c r="H1524" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1525" t="n">
+        <v>8022555</v>
+      </c>
+      <c r="C1525" t="n">
+        <v>369.040008544922</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>345.299987792969</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>368.890014648438</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>368.890014648438</v>
+      </c>
+      <c r="H1525" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -40004,13 +40004,13 @@
         <v>46304.5625</v>
       </c>
       <c r="B1525" t="n">
-        <v>8022555</v>
+        <v>8025600</v>
       </c>
       <c r="C1525" t="n">
         <v>369.040008544922</v>
       </c>
       <c r="D1525" t="n">
-        <v>345.75</v>
+        <v>345.299987792969</v>
       </c>
       <c r="E1525" t="n">
         <v>345.299987792969</v>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -40056,7 +40056,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1527" t="n">
-        <v>4109780</v>
+        <v>4111700</v>
       </c>
       <c r="C1527" t="n">
         <v>368.630004882812</v>
@@ -40074,6 +40074,32 @@
         <v>357.760009765625</v>
       </c>
       <c r="H1527" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1528" t="n">
+        <v>4570205</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>333.910003662109</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>350.529998779297</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>335.079986572266</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>335.079986572266</v>
+      </c>
+      <c r="H1528" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -40082,13 +40082,13 @@
         <v>46309.5625</v>
       </c>
       <c r="B1528" t="n">
-        <v>4570205</v>
+        <v>4594900</v>
       </c>
       <c r="C1528" t="n">
-        <v>356.75</v>
+        <v>356.838989257812</v>
       </c>
       <c r="D1528" t="n">
-        <v>333.910003662109</v>
+        <v>333.709991455078</v>
       </c>
       <c r="E1528" t="n">
         <v>350.529998779297</v>
@@ -40100,6 +40100,32 @@
         <v>335.079986572266</v>
       </c>
       <c r="H1528" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1529" t="n">
+        <v>5676622</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>336.380004882812</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>317.820007324219</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>321.575012207031</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>335.070007324219</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>335.070007324219</v>
+      </c>
+      <c r="H1529" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -40108,7 +40108,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1529" t="n">
-        <v>5676622</v>
+        <v>5678200</v>
       </c>
       <c r="C1529" t="n">
         <v>336.380004882812</v>
@@ -40126,6 +40126,32 @@
         <v>335.070007324219</v>
       </c>
       <c r="H1529" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1530" t="n">
+        <v>8760956</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>343.880004882812</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>302.239990234375</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>339.809997558594</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>306.839996337891</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>306.839996337891</v>
+      </c>
+      <c r="H1530" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44771,9 +44771,38 @@
         <v>315.350006103516</v>
       </c>
       <c r="H1531" t="n">
-        <v>5302846</v>
+        <v>5303900</v>
       </c>
       <c r="I1531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1532" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1532" t="n">
+        <v>311.480010986328</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>323.769989013672</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>319.609985351562</v>
+      </c>
+      <c r="G1532" t="n">
+        <v>319.609985351562</v>
+      </c>
+      <c r="H1532" t="n">
+        <v>4182412</v>
+      </c>
+      <c r="I1532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44800,9 +44800,38 @@
         <v>319.609985351562</v>
       </c>
       <c r="H1532" t="n">
-        <v>4182412</v>
+        <v>4185600</v>
       </c>
       <c r="I1532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1533" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1533" t="n">
+        <v>320.100006103516</v>
+      </c>
+      <c r="D1533" t="n">
+        <v>327.484985351562</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>318.101013183594</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>322.730010986328</v>
+      </c>
+      <c r="G1533" t="n">
+        <v>322.730010986328</v>
+      </c>
+      <c r="H1533" t="n">
+        <v>2561900</v>
+      </c>
+      <c r="I1533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44829,9 +44829,38 @@
         <v>322.730010986328</v>
       </c>
       <c r="H1533" t="n">
-        <v>2561900</v>
+        <v>2595100</v>
       </c>
       <c r="I1533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1534" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1534" t="n">
+        <v>318.890014648438</v>
+      </c>
+      <c r="D1534" t="n">
+        <v>323.790008544922</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>306.850006103516</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>313.959991455078</v>
+      </c>
+      <c r="G1534" t="n">
+        <v>313.959991455078</v>
+      </c>
+      <c r="H1534" t="n">
+        <v>3780267</v>
+      </c>
+      <c r="I1534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44846,7 +44846,7 @@
         <v>318.890014648438</v>
       </c>
       <c r="D1534" t="n">
-        <v>323.790008544922</v>
+        <v>323.940002441406</v>
       </c>
       <c r="E1534" t="n">
         <v>306.850006103516</v>
@@ -44858,9 +44858,38 @@
         <v>313.959991455078</v>
       </c>
       <c r="H1534" t="n">
-        <v>3780267</v>
+        <v>3781100</v>
       </c>
       <c r="I1534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1535" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1535" t="n">
+        <v>310.309997558594</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>325.565002441406</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>310.410003662109</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>325.429992675781</v>
+      </c>
+      <c r="G1535" t="n">
+        <v>325.429992675781</v>
+      </c>
+      <c r="H1535" t="n">
+        <v>3132094</v>
+      </c>
+      <c r="I1535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44875,10 +44875,10 @@
         <v>310.309997558594</v>
       </c>
       <c r="D1535" t="n">
-        <v>325.565002441406</v>
+        <v>325.619995117188</v>
       </c>
       <c r="E1535" t="n">
-        <v>310.410003662109</v>
+        <v>310.309997558594</v>
       </c>
       <c r="F1535" t="n">
         <v>325.429992675781</v>
@@ -44887,9 +44887,38 @@
         <v>325.429992675781</v>
       </c>
       <c r="H1535" t="n">
-        <v>3132094</v>
+        <v>3134500</v>
       </c>
       <c r="I1535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1536" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1536" t="n">
+        <v>324.700012207031</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>337.989990234375</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>322.740112304688</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>334.950012207031</v>
+      </c>
+      <c r="G1536" t="n">
+        <v>334.950012207031</v>
+      </c>
+      <c r="H1536" t="n">
+        <v>2619726</v>
+      </c>
+      <c r="I1536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44907,7 +44907,7 @@
         <v>337.989990234375</v>
       </c>
       <c r="E1536" t="n">
-        <v>322.740112304688</v>
+        <v>322.739990234375</v>
       </c>
       <c r="F1536" t="n">
         <v>334.950012207031</v>
@@ -44916,9 +44916,38 @@
         <v>334.950012207031</v>
       </c>
       <c r="H1536" t="n">
-        <v>2619726</v>
+        <v>2626400</v>
       </c>
       <c r="I1536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1537" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1537" t="n">
+        <v>332.929992675781</v>
+      </c>
+      <c r="D1537" t="n">
+        <v>341.239990234375</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>331.570007324219</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>337.420013427734</v>
+      </c>
+      <c r="G1537" t="n">
+        <v>337.420013427734</v>
+      </c>
+      <c r="H1537" t="n">
+        <v>2310418</v>
+      </c>
+      <c r="I1537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44945,9 +44945,38 @@
         <v>337.420013427734</v>
       </c>
       <c r="H1537" t="n">
-        <v>2310418</v>
+        <v>2311300</v>
       </c>
       <c r="I1537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1538" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1538" t="n">
+        <v>336.019989013672</v>
+      </c>
+      <c r="D1538" t="n">
+        <v>343.549987792969</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>335.020111083984</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>339.910003662109</v>
+      </c>
+      <c r="G1538" t="n">
+        <v>339.910003662109</v>
+      </c>
+      <c r="H1538" t="n">
+        <v>2629469</v>
+      </c>
+      <c r="I1538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44965,7 +44965,7 @@
         <v>343.549987792969</v>
       </c>
       <c r="E1538" t="n">
-        <v>335.020111083984</v>
+        <v>335.019989013672</v>
       </c>
       <c r="F1538" t="n">
         <v>339.910003662109</v>
@@ -44974,9 +44974,38 @@
         <v>339.910003662109</v>
       </c>
       <c r="H1538" t="n">
-        <v>2629469</v>
+        <v>2664400</v>
       </c>
       <c r="I1538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1539" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1539" t="n">
+        <v>327</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>322.799987792969</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>330.269989013672</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>330.269989013672</v>
+      </c>
+      <c r="H1539" t="n">
+        <v>3251532</v>
+      </c>
+      <c r="I1539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SNOW.xlsx
+++ b/data/SNOW.xlsx
@@ -44991,7 +44991,7 @@
         <v>327</v>
       </c>
       <c r="D1539" t="n">
-        <v>338.5</v>
+        <v>338.570007324219</v>
       </c>
       <c r="E1539" t="n">
         <v>322.799987792969</v>
@@ -45003,9 +45003,38 @@
         <v>330.269989013672</v>
       </c>
       <c r="H1539" t="n">
-        <v>3251532</v>
+        <v>3258800</v>
       </c>
       <c r="I1539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1540" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1540" t="n">
+        <v>313.25</v>
+      </c>
+      <c r="D1540" t="n">
+        <v>314.929992675781</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>295.260009765625</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>306.079986572266</v>
+      </c>
+      <c r="G1540" t="n">
+        <v>306.079986572266</v>
+      </c>
+      <c r="H1540" t="n">
+        <v>7747027</v>
+      </c>
+      <c r="I1540" t="s">
         <v>9</v>
       </c>
     </row>
